--- a/client/public/products/pack2-proposal-toolkit/proposal-compliance-matrix.xlsx
+++ b/client/public/products/pack2-proposal-toolkit/proposal-compliance-matrix.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -109,8 +109,47 @@
       <color rgb="FF01696F"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0001696F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -135,8 +174,13 @@
         <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0D1B2A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -159,6 +203,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -170,7 +228,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -276,6 +334,20 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -405,6 +477,107 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Compliance Status</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Compliance Matrix'!$B$42:$B$45</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Compliance Matrix'!$C$42:$C$45</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3960000" cy="2160000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -589,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="B2:P56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="18" min="1" max="1"/>
@@ -604,7 +777,6 @@
     <col width="25" customWidth="1" style="18" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="19">
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -619,7 +791,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="19">
       <c r="B5" s="22" t="inlineStr">
         <is>
@@ -671,9 +842,16 @@
         <f>COUNTIF(I9:I38,"Not Started")</f>
         <v/>
       </c>
-    </row>
-    <row r="6"/>
-    <row r="7"/>
+      <c r="O5" s="36" t="inlineStr">
+        <is>
+          <t>% Complete:</t>
+        </is>
+      </c>
+      <c r="P5" s="37">
+        <f>IF(E5&gt;0,G5/E5,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="8" ht="36" customHeight="1" s="19">
       <c r="B8" s="28" t="inlineStr">
         <is>
@@ -752,10 +930,8 @@
           <t>V - Admin</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F9" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="G9" s="32" t="inlineStr">
         <is>
@@ -799,10 +975,8 @@
           <t>V - Admin</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F10" s="45" t="n">
+        <v>2</v>
       </c>
       <c r="G10" s="32" t="inlineStr">
         <is>
@@ -846,10 +1020,8 @@
           <t>I - Technical</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F11" s="45" t="n">
+        <v>3</v>
       </c>
       <c r="G11" s="32" t="inlineStr">
         <is>
@@ -893,10 +1065,8 @@
           <t>I - Technical</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F12" s="45" t="n">
+        <v>10</v>
       </c>
       <c r="G12" s="32" t="inlineStr">
         <is>
@@ -940,10 +1110,8 @@
           <t>I - Technical</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F13" s="45" t="n">
+        <v>5</v>
       </c>
       <c r="G13" s="32" t="inlineStr">
         <is>
@@ -987,10 +1155,8 @@
           <t>I - Technical</t>
         </is>
       </c>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F14" s="45" t="n">
+        <v>5</v>
       </c>
       <c r="G14" s="32" t="inlineStr">
         <is>
@@ -1034,10 +1200,8 @@
           <t>I - Technical</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F15" s="45" t="n">
+        <v>5</v>
       </c>
       <c r="G15" s="32" t="inlineStr">
         <is>
@@ -1081,10 +1245,8 @@
           <t>I - Technical</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F16" s="45" t="n">
+        <v>3</v>
       </c>
       <c r="G16" s="32" t="inlineStr">
         <is>
@@ -1128,10 +1290,8 @@
           <t>II - Management</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F17" s="45" t="n">
+        <v>5</v>
       </c>
       <c r="G17" s="32" t="inlineStr">
         <is>
@@ -1222,10 +1382,8 @@
           <t>II - Management</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F19" s="45" t="n">
+        <v>5</v>
       </c>
       <c r="G19" s="32" t="inlineStr">
         <is>
@@ -1269,10 +1427,8 @@
           <t>II - Management</t>
         </is>
       </c>
-      <c r="F20" s="32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F20" s="45" t="n">
+        <v>3</v>
       </c>
       <c r="G20" s="32" t="inlineStr">
         <is>
@@ -1316,10 +1472,8 @@
           <t>II - Management</t>
         </is>
       </c>
-      <c r="F21" s="32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F21" s="45" t="n">
+        <v>5</v>
       </c>
       <c r="G21" s="32" t="inlineStr">
         <is>
@@ -1551,10 +1705,8 @@
           <t>IV - Price/Cost</t>
         </is>
       </c>
-      <c r="F26" s="32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F26" s="45" t="n">
+        <v>10</v>
       </c>
       <c r="G26" s="32" t="inlineStr">
         <is>
@@ -1786,10 +1938,8 @@
           <t>V - Admin</t>
         </is>
       </c>
-      <c r="F31" s="32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F31" s="45" t="n">
+        <v>5</v>
       </c>
       <c r="G31" s="32" t="inlineStr">
         <is>
@@ -1833,10 +1983,8 @@
           <t>V - Admin</t>
         </is>
       </c>
-      <c r="F32" s="32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F32" s="45" t="n">
+        <v>2</v>
       </c>
       <c r="G32" s="32" t="inlineStr">
         <is>
@@ -1927,10 +2075,8 @@
           <t>V - Admin</t>
         </is>
       </c>
-      <c r="F34" s="32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F34" s="45" t="n">
+        <v>3</v>
       </c>
       <c r="G34" s="32" t="inlineStr">
         <is>
@@ -1974,10 +2120,8 @@
           <t>II - Management</t>
         </is>
       </c>
-      <c r="F35" s="32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F35" s="45" t="n">
+        <v>2</v>
       </c>
       <c r="G35" s="32" t="inlineStr">
         <is>
@@ -2021,10 +2165,8 @@
           <t>II - Management</t>
         </is>
       </c>
-      <c r="F36" s="32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F36" s="45" t="n">
+        <v>2</v>
       </c>
       <c r="G36" s="32" t="inlineStr">
         <is>
@@ -2068,10 +2210,8 @@
           <t>II - Management</t>
         </is>
       </c>
-      <c r="F37" s="32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F37" s="45" t="n">
+        <v>2</v>
       </c>
       <c r="G37" s="32" t="inlineStr">
         <is>
@@ -2115,10 +2255,8 @@
           <t>II - Management</t>
         </is>
       </c>
-      <c r="F38" s="32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F38" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="G38" s="32" t="inlineStr">
         <is>
@@ -2141,6 +2279,178 @@
         <is>
           <t>Show prime &amp; sub relationships; names on chart</t>
         </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="38" t="inlineStr">
+        <is>
+          <t>STATUS BREAKDOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="39" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="C42" s="39">
+        <f>G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="39" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C43" s="39">
+        <f>I5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="39" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="C44" s="39">
+        <f>K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="C45" s="39">
+        <f>M5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="38" t="inlineStr">
+        <is>
+          <t>PAGE BUDGET BY VOLUME</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="40" t="inlineStr">
+        <is>
+          <t>Sums numeric page limits in column F. Per-instance entries ("2/person", "1/ref") are excluded — count those manually.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="41" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="C50" s="41" t="inlineStr">
+        <is>
+          <t>Page Budget</t>
+        </is>
+      </c>
+      <c r="D50" s="41" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="39" t="inlineStr">
+        <is>
+          <t>I - Technical</t>
+        </is>
+      </c>
+      <c r="C51" s="39">
+        <f>SUMIFS($F$9:$F$38,$E$9:$E$38,$B51)</f>
+        <v/>
+      </c>
+      <c r="D51" s="39">
+        <f>COUNTIFS($E$9:$E$38,$B51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="39" t="inlineStr">
+        <is>
+          <t>II - Management</t>
+        </is>
+      </c>
+      <c r="C52" s="39">
+        <f>SUMIFS($F$9:$F$38,$E$9:$E$38,$B52)</f>
+        <v/>
+      </c>
+      <c r="D52" s="39">
+        <f>COUNTIFS($E$9:$E$38,$B52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="39" t="inlineStr">
+        <is>
+          <t>III - Past Performance</t>
+        </is>
+      </c>
+      <c r="C53" s="39">
+        <f>SUMIFS($F$9:$F$38,$E$9:$E$38,$B53)</f>
+        <v/>
+      </c>
+      <c r="D53" s="39">
+        <f>COUNTIFS($E$9:$E$38,$B53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="39" t="inlineStr">
+        <is>
+          <t>IV - Price/Cost</t>
+        </is>
+      </c>
+      <c r="C54" s="39">
+        <f>SUMIFS($F$9:$F$38,$E$9:$E$38,$B54)</f>
+        <v/>
+      </c>
+      <c r="D54" s="39">
+        <f>COUNTIFS($E$9:$E$38,$B54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="39" t="inlineStr">
+        <is>
+          <t>V - Admin</t>
+        </is>
+      </c>
+      <c r="C55" s="39">
+        <f>SUMIFS($F$9:$F$38,$E$9:$E$38,$B55)</f>
+        <v/>
+      </c>
+      <c r="D55" s="39">
+        <f>COUNTIFS($E$9:$E$38,$B55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="42" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C56" s="42">
+        <f>SUM(C51:C55)</f>
+        <v/>
+      </c>
+      <c r="D56" s="42">
+        <f>SUM(D51:D55)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2180,6 +2490,7 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2190,14 +2501,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="B2:B45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="18" min="1" max="1"/>
     <col width="90" customWidth="1" style="18" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="19">
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2212,8 +2522,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="21.75" customHeight="1" s="19">
       <c r="B6" s="34" t="inlineStr">
         <is>
@@ -2228,7 +2536,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="21.75" customHeight="1" s="19">
       <c r="B9" s="34" t="inlineStr">
         <is>
@@ -2250,7 +2557,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="21.75" customHeight="1" s="19">
       <c r="B13" s="34" t="inlineStr">
         <is>
@@ -2307,7 +2613,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="21.75" customHeight="1" s="19">
       <c r="B22" s="34" t="inlineStr">
         <is>
@@ -2350,7 +2655,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="21.75" customHeight="1" s="19">
       <c r="B29" s="34" t="inlineStr">
         <is>
@@ -2393,7 +2697,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36" ht="21.75" customHeight="1" s="19">
       <c r="B36" s="34" t="inlineStr">
         <is>
@@ -2429,11 +2732,24 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42" ht="18" customHeight="1" s="19">
       <c r="B42" s="35" t="inlineStr">
         <is>
           <t>© Acqlerate — Defense Acquisitions Academy. For training use only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="43" t="inlineStr">
+        <is>
+          <t>License &amp; Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="44" t="inlineStr">
+        <is>
+          <t>This template is licensed for use on one program, by one organization, under your Acqlerate purchase. Customize the text, branding, and layout freely for your own program. Deploying it company-wide, sharing it outside your organization, or reselling it requires an Acqlerate Team License (acqlerate.com/team).</t>
         </is>
       </c>
     </row>

--- a/client/public/products/pack2-proposal-toolkit/proposal-compliance-matrix.xlsx
+++ b/client/public/products/pack2-proposal-toolkit/proposal-compliance-matrix.xlsx
@@ -1960,7 +1960,7 @@
       <c r="K31" s="30" t="n"/>
       <c r="L31" s="30" t="inlineStr">
         <is>
-          <t>Required if contract &gt;$750K; include goals</t>
+          <t>Required above $900K ($2M construction) for other-than-small; include goals</t>
         </is>
       </c>
     </row>
